--- a/StructureDefinition-NgPatient.xlsx
+++ b/StructureDefinition-NgPatient.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$113</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4593" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4220" uniqueCount="679">
   <si>
     <t>Property</t>
   </si>
@@ -27,7 +27,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/StructureDefinition/NgPatient</t>
+    <t>https://www.dhin-hie.org/IGs/StructureDefinition/NgPatient</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-08-02T14:19:18+01:00</t>
+    <t>2025-09-10T08:54:29+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1092,7 +1092,7 @@
     <t>Needed for identification of the individual, in combination with (at least) name and birth date.</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-gender</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-gender</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/administrativeGender</t>
@@ -1366,7 +1366,7 @@
     <t>Madison</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-lgas</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-lgas</t>
   </si>
   <si>
     <t>Address.district</t>
@@ -1391,7 +1391,7 @@
     <t>Sub-unit of a country with limited sovereignty in a federally organized country. A code may be used if codes are in common use (e.g. US 2 letter state codes).</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-states</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-states</t>
   </si>
   <si>
     <t>Address.state</t>
@@ -1553,204 +1553,6 @@
     <t>OBX-5 - needs a profile</t>
   </si>
   <si>
-    <t>Patient.photo.id</t>
-  </si>
-  <si>
-    <t>Patient.photo.extension</t>
-  </si>
-  <si>
-    <t>Patient.photo.contentType</t>
-  </si>
-  <si>
-    <t>Type of image (e.g., image/jpeg)</t>
-  </si>
-  <si>
-    <t>Identifies the type of the data in the attachment and allows a method to be chosen to interpret or render the data. Includes mime type parameters such as charset where appropriate.</t>
-  </si>
-  <si>
-    <t>Processors of the data need to be able to know how to interpret the data.</t>
-  </si>
-  <si>
-    <t>text/plain; charset=UTF-8, image/png</t>
-  </si>
-  <si>
-    <t>The mime type of an attachment. Any valid mime type is allowed.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/mimetypes|4.0.1</t>
-  </si>
-  <si>
-    <t>Attachment.contentType</t>
-  </si>
-  <si>
-    <t>./mediaType, ./charset</t>
-  </si>
-  <si>
-    <t>ED.2+ED.3/RP.2+RP.3. Note conversion may be needed if old style values are being used</t>
-  </si>
-  <si>
-    <t>Patient.photo.language</t>
-  </si>
-  <si>
-    <t>Human language of the content (BCP-47)</t>
-  </si>
-  <si>
-    <t>The human language of the content. The value can be any valid value according to BCP 47.</t>
-  </si>
-  <si>
-    <t>Users need to be able to choose between the languages in a set of attachments.</t>
-  </si>
-  <si>
-    <t>en-AU</t>
-  </si>
-  <si>
-    <t>Attachment.language</t>
-  </si>
-  <si>
-    <t>./language</t>
-  </si>
-  <si>
-    <t>Patient.photo.data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base64Binary
-</t>
-  </si>
-  <si>
-    <t>Base64 encoded image data</t>
-  </si>
-  <si>
-    <t>The actual data of the attachment - a sequence of bytes, base64 encoded.</t>
-  </si>
-  <si>
-    <t>The base64-encoded data SHALL be expressed in the same character set as the base resource XML or JSON.</t>
-  </si>
-  <si>
-    <t>The data needs to able to be transmitted inline.</t>
-  </si>
-  <si>
-    <t>Attachment.data</t>
-  </si>
-  <si>
-    <t>./data</t>
-  </si>
-  <si>
-    <t>ED.5</t>
-  </si>
-  <si>
-    <t>Patient.photo.url</t>
-  </si>
-  <si>
-    <t xml:space="preserve">url
-</t>
-  </si>
-  <si>
-    <t>Public URL or internal endpoint to the patient's photo</t>
-  </si>
-  <si>
-    <t>A location where the data can be accessed.</t>
-  </si>
-  <si>
-    <t>If both data and url are provided, the url SHALL point to the same content as the data contains. Urls may be relative references or may reference transient locations such as a wrapping envelope using cid: though this has ramifications for using signatures. Relative URLs are interpreted relative to the service url, like a resource reference, rather than relative to the resource itself. If a URL is provided, it SHALL resolve to actual data.</t>
-  </si>
-  <si>
-    <t>The data needs to be transmitted by reference.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/logo-small.png</t>
-  </si>
-  <si>
-    <t>Attachment.url</t>
-  </si>
-  <si>
-    <t>./reference/literal</t>
-  </si>
-  <si>
-    <t>RP.1+RP.2 - if they refer to a URL (see v2.6)</t>
-  </si>
-  <si>
-    <t>Patient.photo.size</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unsignedInt
-</t>
-  </si>
-  <si>
-    <t>The size of the image in mega bytes MB</t>
-  </si>
-  <si>
-    <t>The number of bytes of data that make up this attachment (before base64 encoding, if that is done).</t>
-  </si>
-  <si>
-    <t>The number of bytes is redundant if the data is provided as a base64binary, but is useful if the data is provided as a url reference.</t>
-  </si>
-  <si>
-    <t>Representing the size allows applications to determine whether they should fetch the content automatically in advance, or refuse to fetch it at all.</t>
-  </si>
-  <si>
-    <t>Attachment.size</t>
-  </si>
-  <si>
-    <t>N/A (needs data type R3 proposal)</t>
-  </si>
-  <si>
-    <t>Patient.photo.hash</t>
-  </si>
-  <si>
-    <t>Hash of the data (sha-1, base64ed)</t>
-  </si>
-  <si>
-    <t>The calculated hash of the data using SHA-1. Represented using base64.</t>
-  </si>
-  <si>
-    <t>The hash is calculated on the data prior to base64 encoding, if the data is based64 encoded. The hash is not intended to support digital signatures. Where protection against malicious threats a digital signature should be considered, see [Provenance.signature](http://hl7.org/fhir/R4/provenance-definitions.html#Provenance.signature) for mechanism to protect a resource with a digital signature.</t>
-  </si>
-  <si>
-    <t>Included so that applications can verify that the contents of a location have not changed due to technical failures (e.g., storage rot, transport glitch, incorrect version).</t>
-  </si>
-  <si>
-    <t>Attachment.hash</t>
-  </si>
-  <si>
-    <t>.integrityCheck[parent::ED/integrityCheckAlgorithm="SHA-1"]</t>
-  </si>
-  <si>
-    <t>Patient.photo.title</t>
-  </si>
-  <si>
-    <t>The label of the image</t>
-  </si>
-  <si>
-    <t>A label or set of text to display in place of the data.</t>
-  </si>
-  <si>
-    <t>Applications need a label to display to a human user in place of the actual data if the data cannot be rendered or perceived by the viewer.</t>
-  </si>
-  <si>
-    <t>Official Corporate Logo</t>
-  </si>
-  <si>
-    <t>Attachment.title</t>
-  </si>
-  <si>
-    <t>./title/data</t>
-  </si>
-  <si>
-    <t>Patient.photo.creation</t>
-  </si>
-  <si>
-    <t>Date attachment was first created</t>
-  </si>
-  <si>
-    <t>The date that the attachment was first created.</t>
-  </si>
-  <si>
-    <t>This is often tracked as an integrity issue for use of the attachment.</t>
-  </si>
-  <si>
-    <t>Attachment.creation</t>
-  </si>
-  <si>
     <t>Patient.contact</t>
   </si>
   <si>
@@ -2172,7 +1974,7 @@
     <t>Most systems in multilingual countries will want to convey language. Not all systems actually need the regional dialect.</t>
   </si>
   <si>
-    <t>https://dhin.org/2025Connectathon/ValueSet/nigeria-languages</t>
+    <t>https://www.dhin-hie.org/IGs/ValueSet/nigeria-languages</t>
   </si>
   <si>
     <t>player[classCode=PSN|ANM and determinerCode=INSTANCE]/languageCommunication/code</t>
@@ -2639,7 +2441,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO123"/>
+  <dimension ref="A1:AO113"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="32.95703125" customWidth="true" bestFit="true"/>
@@ -2667,7 +2469,7 @@
     <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="82.29296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="51.3203125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="46.40625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
@@ -5982,7 +5784,7 @@
         <v>90</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>91</v>
@@ -9618,7 +9420,7 @@
         <v>81</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>82</v>
@@ -9734,10 +9536,10 @@
         <v>80</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>82</v>
@@ -9746,16 +9548,20 @@
         <v>82</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>104</v>
+        <v>496</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>105</v>
+        <v>497</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N61" s="2"/>
-      <c r="O61" s="2"/>
+        <v>498</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="O61" t="s" s="2">
+        <v>500</v>
+      </c>
       <c r="P61" t="s" s="2">
         <v>82</v>
       </c>
@@ -9803,25 +9609,25 @@
         <v>82</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>107</v>
+        <v>495</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>82</v>
+        <v>501</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AL61" t="s" s="2">
         <v>108</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>82</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>82</v>
@@ -9835,21 +9641,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>82</v>
@@ -9861,17 +9667,15 @@
         <v>82</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>82</v>
@@ -9908,31 +9712,31 @@
         <v>82</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>108</v>
@@ -9952,21 +9756,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>82</v>
@@ -9975,21 +9779,21 @@
         <v>82</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>498</v>
+        <v>112</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>499</v>
-      </c>
-      <c r="N63" s="2"/>
-      <c r="O63" t="s" s="2">
-        <v>500</v>
-      </c>
+        <v>113</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>82</v>
       </c>
@@ -10001,7 +9805,7 @@
         <v>82</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>501</v>
+        <v>82</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>82</v>
@@ -10013,13 +9817,13 @@
         <v>82</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>502</v>
+        <v>82</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>503</v>
+        <v>82</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>82</v>
@@ -10037,22 +9841,22 @@
         <v>82</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>504</v>
+        <v>118</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>505</v>
+        <v>108</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>82</v>
@@ -10061,7 +9865,7 @@
         <v>82</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>506</v>
+        <v>82</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>82</v>
@@ -10069,10 +9873,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10083,30 +9887,28 @@
         <v>80</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J64" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>166</v>
+        <v>111</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>508</v>
+        <v>194</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>509</v>
+        <v>195</v>
       </c>
       <c r="N64" s="2"/>
-      <c r="O64" t="s" s="2">
-        <v>510</v>
-      </c>
+      <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
         <v>82</v>
       </c>
@@ -10118,7 +9920,7 @@
         <v>82</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>511</v>
+        <v>82</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>82</v>
@@ -10130,13 +9932,13 @@
         <v>82</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>170</v>
+        <v>82</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>171</v>
+        <v>82</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>82</v>
@@ -10154,22 +9956,22 @@
         <v>82</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>513</v>
+        <v>82</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>82</v>
@@ -10186,10 +9988,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>514</v>
+        <v>507</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10200,7 +10002,7 @@
         <v>80</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>82</v>
@@ -10212,19 +10014,17 @@
         <v>82</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>515</v>
+        <v>219</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>518</v>
-      </c>
+        <v>509</v>
+      </c>
+      <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>82</v>
@@ -10249,13 +10049,13 @@
         <v>82</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>82</v>
+        <v>148</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>82</v>
+        <v>511</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>82</v>
+        <v>512</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>82</v>
@@ -10273,13 +10073,13 @@
         <v>82</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>82</v>
@@ -10288,16 +10088,16 @@
         <v>102</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>82</v>
@@ -10305,10 +10105,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10328,22 +10128,20 @@
         <v>82</v>
       </c>
       <c r="J66" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>524</v>
+        <v>270</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="N66" t="s" s="2">
-        <v>527</v>
-      </c>
+        <v>517</v>
+      </c>
+      <c r="N66" s="2"/>
       <c r="O66" t="s" s="2">
-        <v>528</v>
+        <v>518</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>82</v>
@@ -10356,7 +10154,7 @@
         <v>82</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>529</v>
+        <v>82</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>82</v>
@@ -10392,7 +10190,7 @@
         <v>82</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>530</v>
+        <v>515</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10407,16 +10205,16 @@
         <v>102</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>531</v>
+        <v>275</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>82</v>
@@ -10424,10 +10222,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10447,23 +10245,19 @@
         <v>82</v>
       </c>
       <c r="J67" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>534</v>
+        <v>104</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>535</v>
+        <v>105</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N67" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>538</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
         <v>82</v>
       </c>
@@ -10511,7 +10305,7 @@
         <v>82</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>539</v>
+        <v>107</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -10523,10 +10317,10 @@
         <v>82</v>
       </c>
       <c r="AJ67" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>540</v>
+        <v>108</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>82</v>
@@ -10543,21 +10337,21 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>541</v>
+        <v>521</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H68" t="s" s="2">
         <v>82</v>
@@ -10566,23 +10360,21 @@
         <v>82</v>
       </c>
       <c r="J68" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>515</v>
+        <v>111</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>542</v>
+        <v>112</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>543</v>
+        <v>113</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>545</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
         <v>82</v>
       </c>
@@ -10618,34 +10410,34 @@
         <v>82</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC68" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>546</v>
+        <v>118</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ68" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>547</v>
+        <v>108</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>82</v>
@@ -10662,10 +10454,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>548</v>
+        <v>522</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10676,29 +10468,31 @@
         <v>80</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I69" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J69" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>549</v>
+        <v>281</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>282</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>283</v>
+      </c>
       <c r="O69" t="s" s="2">
-        <v>551</v>
+        <v>284</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>82</v>
@@ -10711,7 +10505,7 @@
         <v>82</v>
       </c>
       <c r="T69" t="s" s="2">
-        <v>552</v>
+        <v>82</v>
       </c>
       <c r="U69" t="s" s="2">
         <v>82</v>
@@ -10723,13 +10517,13 @@
         <v>82</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>82</v>
+        <v>285</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>82</v>
+        <v>286</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>82</v>
@@ -10747,7 +10541,7 @@
         <v>82</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>553</v>
+        <v>287</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -10762,7 +10556,7 @@
         <v>102</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>554</v>
+        <v>288</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>82</v>
@@ -10771,7 +10565,7 @@
         <v>82</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>82</v>
+        <v>289</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>82</v>
@@ -10779,10 +10573,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>555</v>
+        <v>523</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10805,17 +10599,19 @@
         <v>91</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>376</v>
+        <v>104</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>556</v>
+        <v>291</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="N70" s="2"/>
+        <v>292</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>293</v>
+      </c>
       <c r="O70" t="s" s="2">
-        <v>558</v>
+        <v>294</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>82</v>
@@ -10864,7 +10660,7 @@
         <v>82</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>559</v>
+        <v>295</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10879,7 +10675,7 @@
         <v>102</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>540</v>
+        <v>296</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>82</v>
@@ -10888,7 +10684,7 @@
         <v>82</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>82</v>
+        <v>297</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>82</v>
@@ -10896,46 +10692,44 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>560</v>
+        <v>524</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>560</v>
+        <v>524</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>82</v>
+        <v>299</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="J71" t="s" s="2">
         <v>91</v>
       </c>
-      <c r="I71" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J71" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="K71" t="s" s="2">
-        <v>561</v>
+        <v>104</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>562</v>
+        <v>525</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>563</v>
+        <v>301</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>565</v>
-      </c>
+        <v>302</v>
+      </c>
+      <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
         <v>82</v>
       </c>
@@ -10983,31 +10777,31 @@
         <v>82</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>560</v>
+        <v>303</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>566</v>
+        <v>102</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>567</v>
+        <v>304</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>82</v>
+        <v>305</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>82</v>
@@ -11015,21 +10809,21 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>568</v>
+        <v>526</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>568</v>
+        <v>526</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="E72" s="2"/>
       <c r="F72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H72" t="s" s="2">
         <v>82</v>
@@ -11038,18 +10832,20 @@
         <v>82</v>
       </c>
       <c r="J72" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K72" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>105</v>
+        <v>527</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N72" s="2"/>
+        <v>309</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>310</v>
+      </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>82</v>
@@ -11098,22 +10894,22 @@
         <v>82</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>107</v>
+        <v>311</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>108</v>
+        <v>312</v>
       </c>
       <c r="AL72" t="s" s="2">
         <v>82</v>
@@ -11122,7 +10918,7 @@
         <v>82</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>82</v>
+        <v>313</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>82</v>
@@ -11130,14 +10926,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>569</v>
+        <v>528</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -11153,20 +10949,18 @@
         <v>82</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>112</v>
+        <v>315</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>316</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
         <v>82</v>
@@ -11215,7 +11009,7 @@
         <v>82</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>118</v>
+        <v>317</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -11227,10 +11021,10 @@
         <v>82</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>108</v>
+        <v>318</v>
       </c>
       <c r="AL73" t="s" s="2">
         <v>82</v>
@@ -11239,7 +11033,7 @@
         <v>82</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>82</v>
+        <v>319</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>82</v>
@@ -11247,10 +11041,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>570</v>
+        <v>529</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11261,25 +11055,25 @@
         <v>80</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I74" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J74" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>194</v>
+        <v>321</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>195</v>
+        <v>322</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11330,7 +11124,7 @@
         <v>82</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>571</v>
+        <v>323</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -11342,10 +11136,10 @@
         <v>82</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK74" t="s" s="2">
-        <v>82</v>
+        <v>324</v>
       </c>
       <c r="AL74" t="s" s="2">
         <v>82</v>
@@ -11354,7 +11148,7 @@
         <v>82</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>82</v>
+        <v>325</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>82</v>
@@ -11362,10 +11156,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11376,7 +11170,7 @@
         <v>80</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>82</v>
@@ -11385,20 +11179,20 @@
         <v>82</v>
       </c>
       <c r="J75" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>219</v>
+        <v>246</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>573</v>
+        <v>327</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>574</v>
+        <v>328</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>575</v>
+        <v>329</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>82</v>
@@ -11423,13 +11217,13 @@
         <v>82</v>
       </c>
       <c r="X75" t="s" s="2">
-        <v>148</v>
+        <v>82</v>
       </c>
       <c r="Y75" t="s" s="2">
-        <v>576</v>
+        <v>82</v>
       </c>
       <c r="Z75" t="s" s="2">
-        <v>577</v>
+        <v>82</v>
       </c>
       <c r="AA75" t="s" s="2">
         <v>82</v>
@@ -11447,13 +11241,13 @@
         <v>82</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>572</v>
+        <v>330</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>82</v>
@@ -11462,16 +11256,16 @@
         <v>102</v>
       </c>
       <c r="AK75" t="s" s="2">
-        <v>578</v>
+        <v>331</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>579</v>
+        <v>332</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>82</v>
@@ -11479,10 +11273,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11493,10 +11287,10 @@
         <v>80</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>82</v>
@@ -11505,17 +11299,19 @@
         <v>82</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>270</v>
+        <v>334</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>581</v>
+        <v>532</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="N76" s="2"/>
+        <v>533</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>534</v>
+      </c>
       <c r="O76" t="s" s="2">
-        <v>583</v>
+        <v>338</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>82</v>
@@ -11564,13 +11360,13 @@
         <v>82</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>580</v>
+        <v>531</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>82</v>
@@ -11579,7 +11375,7 @@
         <v>102</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>275</v>
+        <v>339</v>
       </c>
       <c r="AL76" t="s" s="2">
         <v>108</v>
@@ -11588,7 +11384,7 @@
         <v>82</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>584</v>
+        <v>535</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>82</v>
@@ -11596,10 +11392,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>585</v>
+        <v>536</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11711,10 +11507,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>586</v>
+        <v>537</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11828,10 +11624,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>587</v>
+        <v>538</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>587</v>
+        <v>538</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11842,13 +11638,13 @@
         <v>80</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I79" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J79" t="s" s="2">
         <v>91</v>
@@ -11857,17 +11653,13 @@
         <v>166</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>281</v>
+        <v>539</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="N79" t="s" s="2">
-        <v>283</v>
-      </c>
-      <c r="O79" t="s" s="2">
-        <v>284</v>
-      </c>
+        <v>540</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>82</v>
       </c>
@@ -11894,10 +11686,10 @@
         <v>213</v>
       </c>
       <c r="Y79" t="s" s="2">
-        <v>285</v>
+        <v>541</v>
       </c>
       <c r="Z79" t="s" s="2">
-        <v>286</v>
+        <v>542</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>82</v>
@@ -11915,7 +11707,7 @@
         <v>82</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>287</v>
+        <v>543</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -11924,13 +11716,13 @@
         <v>90</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>82</v>
+        <v>544</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>288</v>
+        <v>545</v>
       </c>
       <c r="AL79" t="s" s="2">
         <v>82</v>
@@ -11939,7 +11731,7 @@
         <v>82</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>289</v>
+        <v>546</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>82</v>
@@ -11947,10 +11739,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>588</v>
+        <v>547</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>588</v>
+        <v>547</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11976,16 +11768,16 @@
         <v>104</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>291</v>
+        <v>548</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>292</v>
+        <v>549</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>293</v>
+        <v>550</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>294</v>
+        <v>551</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>82</v>
@@ -12034,7 +11826,7 @@
         <v>82</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>295</v>
+        <v>552</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -12049,7 +11841,7 @@
         <v>102</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>296</v>
+        <v>553</v>
       </c>
       <c r="AL80" t="s" s="2">
         <v>82</v>
@@ -12058,7 +11850,7 @@
         <v>82</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>297</v>
+        <v>554</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>82</v>
@@ -12066,44 +11858,46 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>589</v>
+        <v>555</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>589</v>
+        <v>555</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>299</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I81" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J81" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>590</v>
+        <v>556</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>301</v>
+        <v>557</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="O81" s="2"/>
+        <v>558</v>
+      </c>
+      <c r="O81" t="s" s="2">
+        <v>559</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>82</v>
       </c>
@@ -12127,13 +11921,13 @@
         <v>82</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>82</v>
+        <v>560</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>82</v>
+        <v>561</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>82</v>
@@ -12151,7 +11945,7 @@
         <v>82</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>303</v>
+        <v>562</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12166,7 +11960,7 @@
         <v>102</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="AL81" t="s" s="2">
         <v>82</v>
@@ -12175,7 +11969,7 @@
         <v>82</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>305</v>
+        <v>563</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>82</v>
@@ -12183,21 +11977,21 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>591</v>
+        <v>564</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>307</v>
+        <v>82</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>82</v>
@@ -12209,16 +12003,16 @@
         <v>91</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>104</v>
+        <v>565</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>592</v>
+        <v>566</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>309</v>
+        <v>567</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>310</v>
+        <v>568</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12268,13 +12062,13 @@
         <v>82</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>311</v>
+        <v>569</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>82</v>
@@ -12283,7 +12077,7 @@
         <v>102</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>312</v>
+        <v>108</v>
       </c>
       <c r="AL82" t="s" s="2">
         <v>82</v>
@@ -12292,7 +12086,7 @@
         <v>82</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>313</v>
+        <v>108</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>82</v>
@@ -12300,10 +12094,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>593</v>
+        <v>570</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12314,7 +12108,7 @@
         <v>80</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>82</v>
@@ -12326,13 +12120,13 @@
         <v>91</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>315</v>
+        <v>571</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>316</v>
+        <v>572</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12383,13 +12177,13 @@
         <v>82</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>317</v>
+        <v>573</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>82</v>
@@ -12398,7 +12192,7 @@
         <v>102</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>82</v>
@@ -12407,7 +12201,7 @@
         <v>82</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>319</v>
+        <v>189</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>82</v>
@@ -12415,10 +12209,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12429,7 +12223,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>82</v>
@@ -12438,19 +12232,21 @@
         <v>82</v>
       </c>
       <c r="J84" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>104</v>
+        <v>379</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>321</v>
+        <v>575</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>322</v>
+        <v>576</v>
       </c>
       <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
+      <c r="O84" t="s" s="2">
+        <v>577</v>
+      </c>
       <c r="P84" t="s" s="2">
         <v>82</v>
       </c>
@@ -12498,13 +12294,13 @@
         <v>82</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>323</v>
+        <v>574</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH84" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI84" t="s" s="2">
         <v>82</v>
@@ -12513,16 +12309,16 @@
         <v>102</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>324</v>
+        <v>384</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>325</v>
+        <v>578</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>82</v>
@@ -12530,10 +12326,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12553,21 +12349,19 @@
         <v>82</v>
       </c>
       <c r="J85" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>327</v>
+        <v>105</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>328</v>
+        <v>106</v>
       </c>
       <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>329</v>
-      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>82</v>
       </c>
@@ -12615,7 +12409,7 @@
         <v>82</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>330</v>
+        <v>107</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -12627,10 +12421,10 @@
         <v>82</v>
       </c>
       <c r="AJ85" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>331</v>
+        <v>108</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>82</v>
@@ -12639,7 +12433,7 @@
         <v>82</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>332</v>
+        <v>82</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>82</v>
@@ -12647,14 +12441,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>596</v>
+        <v>580</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -12664,7 +12458,7 @@
         <v>81</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>82</v>
@@ -12673,20 +12467,18 @@
         <v>82</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>334</v>
+        <v>111</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>597</v>
+        <v>112</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>598</v>
+        <v>113</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>338</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>82</v>
       </c>
@@ -12722,19 +12514,19 @@
         <v>82</v>
       </c>
       <c r="AB86" t="s" s="2">
-        <v>82</v>
+        <v>115</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>82</v>
+        <v>116</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>596</v>
+        <v>118</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -12746,19 +12538,19 @@
         <v>82</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>339</v>
+        <v>108</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>600</v>
+        <v>82</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>82</v>
@@ -12766,10 +12558,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12780,28 +12572,32 @@
         <v>80</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I87" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>105</v>
+        <v>390</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+        <v>391</v>
+      </c>
+      <c r="N87" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="O87" t="s" s="2">
+        <v>393</v>
+      </c>
       <c r="P87" t="s" s="2">
         <v>82</v>
       </c>
@@ -12813,7 +12609,7 @@
         <v>82</v>
       </c>
       <c r="T87" t="s" s="2">
-        <v>82</v>
+        <v>394</v>
       </c>
       <c r="U87" t="s" s="2">
         <v>82</v>
@@ -12825,13 +12621,13 @@
         <v>82</v>
       </c>
       <c r="X87" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Y87" t="s" s="2">
-        <v>82</v>
+        <v>395</v>
       </c>
       <c r="Z87" t="s" s="2">
-        <v>82</v>
+        <v>396</v>
       </c>
       <c r="AA87" t="s" s="2">
         <v>82</v>
@@ -12849,7 +12645,7 @@
         <v>82</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>107</v>
+        <v>397</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -12861,10 +12657,10 @@
         <v>82</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="AL87" t="s" s="2">
         <v>82</v>
@@ -12873,7 +12669,7 @@
         <v>82</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>82</v>
+        <v>398</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>82</v>
@@ -12881,21 +12677,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>82</v>
@@ -12904,19 +12700,19 @@
         <v>82</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>112</v>
+        <v>400</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>113</v>
+        <v>401</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>114</v>
+        <v>402</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12930,7 +12726,7 @@
         <v>82</v>
       </c>
       <c r="T88" t="s" s="2">
-        <v>82</v>
+        <v>403</v>
       </c>
       <c r="U88" t="s" s="2">
         <v>82</v>
@@ -12942,46 +12738,46 @@
         <v>82</v>
       </c>
       <c r="X88" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>82</v>
+        <v>404</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>82</v>
+        <v>405</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>118</v>
+        <v>406</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>108</v>
+        <v>288</v>
       </c>
       <c r="AL88" t="s" s="2">
         <v>82</v>
@@ -12990,7 +12786,7 @@
         <v>82</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>82</v>
+        <v>407</v>
       </c>
       <c r="AO88" t="s" s="2">
         <v>82</v>
@@ -12998,10 +12794,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -13024,16 +12820,20 @@
         <v>91</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>604</v>
+        <v>409</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="O89" t="s" s="2">
+        <v>294</v>
+      </c>
       <c r="P89" t="s" s="2">
         <v>82</v>
       </c>
@@ -13045,7 +12845,7 @@
         <v>82</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>82</v>
+        <v>412</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>82</v>
@@ -13057,13 +12857,13 @@
         <v>82</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>606</v>
+        <v>82</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>607</v>
+        <v>82</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>82</v>
@@ -13081,7 +12881,7 @@
         <v>82</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>608</v>
+        <v>413</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13090,13 +12890,13 @@
         <v>90</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>609</v>
+        <v>82</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>610</v>
+        <v>296</v>
       </c>
       <c r="AL89" t="s" s="2">
         <v>82</v>
@@ -13105,7 +12905,7 @@
         <v>82</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>611</v>
+        <v>414</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>82</v>
@@ -13113,10 +12913,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>612</v>
+        <v>584</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13130,7 +12930,7 @@
         <v>90</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>82</v>
@@ -13142,17 +12942,13 @@
         <v>104</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>613</v>
+        <v>585</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>616</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>82</v>
       </c>
@@ -13164,7 +12960,7 @@
         <v>82</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>82</v>
+        <v>418</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>82</v>
@@ -13200,13 +12996,13 @@
         <v>82</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>617</v>
+        <v>419</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH90" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI90" t="s" s="2">
         <v>82</v>
@@ -13215,7 +13011,7 @@
         <v>102</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>618</v>
+        <v>420</v>
       </c>
       <c r="AL90" t="s" s="2">
         <v>82</v>
@@ -13224,7 +13020,7 @@
         <v>82</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>619</v>
+        <v>421</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>82</v>
@@ -13232,46 +13028,42 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>620</v>
+        <v>586</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I91" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J91" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>621</v>
+        <v>587</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="N91" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>624</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>82</v>
       </c>
@@ -13283,7 +13075,7 @@
         <v>82</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>82</v>
+        <v>426</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>82</v>
@@ -13295,13 +13087,13 @@
         <v>82</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>625</v>
+        <v>82</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>626</v>
+        <v>82</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>82</v>
@@ -13319,7 +13111,7 @@
         <v>82</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>627</v>
+        <v>427</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13334,7 +13126,7 @@
         <v>102</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>288</v>
+        <v>428</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>82</v>
@@ -13343,7 +13135,7 @@
         <v>82</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>628</v>
+        <v>429</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>82</v>
@@ -13351,14 +13143,14 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>629</v>
+        <v>588</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>629</v>
+        <v>588</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
-        <v>82</v>
+        <v>431</v>
       </c>
       <c r="E92" s="2"/>
       <c r="F92" t="s" s="2">
@@ -13377,16 +13169,16 @@
         <v>91</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>630</v>
+        <v>104</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>631</v>
+        <v>589</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>632</v>
+        <v>590</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>633</v>
+        <v>434</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -13400,7 +13192,7 @@
         <v>82</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>82</v>
+        <v>435</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>82</v>
@@ -13412,13 +13204,11 @@
         <v>82</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y92" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Y92" s="2"/>
       <c r="Z92" t="s" s="2">
-        <v>82</v>
+        <v>436</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>82</v>
@@ -13436,7 +13226,7 @@
         <v>82</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>634</v>
+        <v>437</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13451,7 +13241,7 @@
         <v>102</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>108</v>
+        <v>438</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>82</v>
@@ -13460,7 +13250,7 @@
         <v>82</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>108</v>
+        <v>439</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>82</v>
@@ -13468,14 +13258,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>635</v>
+        <v>591</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>635</v>
+        <v>591</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>82</v>
+        <v>441</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13494,13 +13284,13 @@
         <v>91</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>636</v>
+        <v>592</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>637</v>
+        <v>443</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13527,13 +13317,11 @@
         <v>82</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y93" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="Y93" s="2"/>
       <c r="Z93" t="s" s="2">
-        <v>82</v>
+        <v>444</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>82</v>
@@ -13551,7 +13339,7 @@
         <v>82</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>638</v>
+        <v>445</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13566,7 +13354,7 @@
         <v>102</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>331</v>
+        <v>446</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>82</v>
@@ -13575,7 +13363,7 @@
         <v>82</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>189</v>
+        <v>447</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>82</v>
@@ -13583,14 +13371,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>639</v>
+        <v>593</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>639</v>
+        <v>593</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>82</v>
+        <v>449</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13606,21 +13394,19 @@
         <v>82</v>
       </c>
       <c r="J94" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>379</v>
+        <v>104</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>640</v>
+        <v>450</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>641</v>
+        <v>451</v>
       </c>
       <c r="N94" s="2"/>
-      <c r="O94" t="s" s="2">
-        <v>642</v>
-      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>82</v>
       </c>
@@ -13632,7 +13418,7 @@
         <v>82</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>82</v>
+        <v>452</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>82</v>
@@ -13668,7 +13454,7 @@
         <v>82</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>639</v>
+        <v>453</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13683,16 +13469,16 @@
         <v>102</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>384</v>
+        <v>454</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>643</v>
+        <v>455</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>82</v>
@@ -13700,10 +13486,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>644</v>
+        <v>594</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>644</v>
+        <v>594</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13723,18 +13509,20 @@
         <v>82</v>
       </c>
       <c r="J95" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K95" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>105</v>
+        <v>457</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>458</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>459</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>82</v>
@@ -13783,7 +13571,7 @@
         <v>82</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>107</v>
+        <v>460</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>80</v>
@@ -13795,10 +13583,10 @@
         <v>82</v>
       </c>
       <c r="AJ95" t="s" s="2">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>108</v>
+        <v>461</v>
       </c>
       <c r="AL95" t="s" s="2">
         <v>82</v>
@@ -13807,7 +13595,7 @@
         <v>82</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>82</v>
+        <v>462</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>82</v>
@@ -13815,21 +13603,21 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>645</v>
+        <v>595</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>645</v>
+        <v>595</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>82</v>
@@ -13838,21 +13626,21 @@
         <v>82</v>
       </c>
       <c r="J96" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>111</v>
+        <v>246</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>112</v>
+        <v>464</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O96" s="2"/>
+        <v>465</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" t="s" s="2">
+        <v>466</v>
+      </c>
       <c r="P96" t="s" s="2">
         <v>82</v>
       </c>
@@ -13864,7 +13652,7 @@
         <v>82</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>82</v>
+        <v>467</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>82</v>
@@ -13888,34 +13676,34 @@
         <v>82</v>
       </c>
       <c r="AB96" t="s" s="2">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="AC96" t="s" s="2">
-        <v>116</v>
+        <v>82</v>
       </c>
       <c r="AD96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AE96" t="s" s="2">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>118</v>
+        <v>468</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ96" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>108</v>
+        <v>331</v>
       </c>
       <c r="AL96" t="s" s="2">
         <v>82</v>
@@ -13924,7 +13712,7 @@
         <v>82</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>82</v>
+        <v>469</v>
       </c>
       <c r="AO96" t="s" s="2">
         <v>82</v>
@@ -13932,10 +13720,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>646</v>
+        <v>596</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>646</v>
+        <v>596</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13946,31 +13734,29 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I97" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K97" t="s" s="2">
         <v>166</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>390</v>
+        <v>597</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>392</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>393</v>
+        <v>599</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>82</v>
@@ -13983,7 +13769,7 @@
         <v>82</v>
       </c>
       <c r="T97" t="s" s="2">
-        <v>394</v>
+        <v>82</v>
       </c>
       <c r="U97" t="s" s="2">
         <v>82</v>
@@ -13998,10 +13784,10 @@
         <v>213</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>395</v>
+        <v>600</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>396</v>
+        <v>601</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>82</v>
@@ -14019,7 +13805,7 @@
         <v>82</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>397</v>
+        <v>596</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>80</v>
@@ -14034,16 +13820,16 @@
         <v>102</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>288</v>
+        <v>348</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>398</v>
+        <v>602</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>82</v>
@@ -14051,10 +13837,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>647</v>
+        <v>603</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>647</v>
+        <v>603</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14074,21 +13860,21 @@
         <v>82</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>400</v>
+        <v>604</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="N98" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="O98" s="2"/>
+        <v>605</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>606</v>
+      </c>
       <c r="P98" t="s" s="2">
         <v>82</v>
       </c>
@@ -14100,7 +13886,7 @@
         <v>82</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>403</v>
+        <v>82</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>82</v>
@@ -14112,13 +13898,13 @@
         <v>82</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>404</v>
+        <v>82</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>405</v>
+        <v>82</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>82</v>
@@ -14136,7 +13922,7 @@
         <v>82</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>406</v>
+        <v>603</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>80</v>
@@ -14145,22 +13931,22 @@
         <v>90</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>82</v>
+        <v>607</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>288</v>
+        <v>608</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>407</v>
+        <v>609</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>82</v>
@@ -14168,10 +13954,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>648</v>
+        <v>610</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>648</v>
+        <v>610</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14191,23 +13977,19 @@
         <v>82</v>
       </c>
       <c r="J99" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>409</v>
+        <v>611</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="O99" t="s" s="2">
-        <v>294</v>
-      </c>
+        <v>612</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
         <v>82</v>
       </c>
@@ -14219,7 +14001,7 @@
         <v>82</v>
       </c>
       <c r="T99" t="s" s="2">
-        <v>412</v>
+        <v>82</v>
       </c>
       <c r="U99" t="s" s="2">
         <v>82</v>
@@ -14255,7 +14037,7 @@
         <v>82</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>413</v>
+        <v>610</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>80</v>
@@ -14270,16 +14052,16 @@
         <v>102</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>296</v>
+        <v>613</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>414</v>
+        <v>82</v>
       </c>
       <c r="AO99" t="s" s="2">
         <v>82</v>
@@ -14287,10 +14069,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>649</v>
+        <v>614</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>649</v>
+        <v>614</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14301,28 +14083,32 @@
         <v>80</v>
       </c>
       <c r="G100" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H100" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="I100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="J100" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>104</v>
+        <v>496</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>650</v>
+        <v>615</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>417</v>
-      </c>
-      <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+        <v>616</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>618</v>
+      </c>
       <c r="P100" t="s" s="2">
         <v>82</v>
       </c>
@@ -14334,7 +14120,7 @@
         <v>82</v>
       </c>
       <c r="T100" t="s" s="2">
-        <v>418</v>
+        <v>82</v>
       </c>
       <c r="U100" t="s" s="2">
         <v>82</v>
@@ -14370,7 +14156,7 @@
         <v>82</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>419</v>
+        <v>614</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>80</v>
@@ -14385,16 +14171,16 @@
         <v>102</v>
       </c>
       <c r="AK100" t="s" s="2">
-        <v>420</v>
+        <v>619</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>82</v>
+        <v>620</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>421</v>
+        <v>82</v>
       </c>
       <c r="AO100" t="s" s="2">
         <v>82</v>
@@ -14402,14 +14188,14 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>651</v>
+        <v>621</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
-        <v>423</v>
+        <v>82</v>
       </c>
       <c r="E101" s="2"/>
       <c r="F101" t="s" s="2">
@@ -14425,16 +14211,16 @@
         <v>82</v>
       </c>
       <c r="J101" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K101" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>652</v>
+        <v>105</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>425</v>
+        <v>106</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14449,7 +14235,7 @@
         <v>82</v>
       </c>
       <c r="T101" t="s" s="2">
-        <v>426</v>
+        <v>82</v>
       </c>
       <c r="U101" t="s" s="2">
         <v>82</v>
@@ -14485,7 +14271,7 @@
         <v>82</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>427</v>
+        <v>107</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14497,10 +14283,10 @@
         <v>82</v>
       </c>
       <c r="AJ101" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK101" t="s" s="2">
-        <v>428</v>
+        <v>108</v>
       </c>
       <c r="AL101" t="s" s="2">
         <v>82</v>
@@ -14509,7 +14295,7 @@
         <v>82</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>429</v>
+        <v>82</v>
       </c>
       <c r="AO101" t="s" s="2">
         <v>82</v>
@@ -14517,21 +14303,21 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>653</v>
+        <v>622</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>653</v>
+        <v>622</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
-        <v>431</v>
+        <v>110</v>
       </c>
       <c r="E102" s="2"/>
       <c r="F102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>82</v>
@@ -14540,19 +14326,19 @@
         <v>82</v>
       </c>
       <c r="J102" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>654</v>
+        <v>112</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>655</v>
+        <v>113</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>434</v>
+        <v>114</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -14566,7 +14352,7 @@
         <v>82</v>
       </c>
       <c r="T102" t="s" s="2">
-        <v>435</v>
+        <v>82</v>
       </c>
       <c r="U102" t="s" s="2">
         <v>82</v>
@@ -14578,11 +14364,13 @@
         <v>82</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y102" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z102" t="s" s="2">
-        <v>436</v>
+        <v>82</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>82</v>
@@ -14600,22 +14388,22 @@
         <v>82</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>437</v>
+        <v>118</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH102" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>438</v>
+        <v>108</v>
       </c>
       <c r="AL102" t="s" s="2">
         <v>82</v>
@@ -14624,7 +14412,7 @@
         <v>82</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>439</v>
+        <v>82</v>
       </c>
       <c r="AO102" t="s" s="2">
         <v>82</v>
@@ -14632,42 +14420,46 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>656</v>
+        <v>623</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>656</v>
+        <v>623</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>441</v>
+        <v>624</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I103" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J103" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>657</v>
+        <v>625</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>443</v>
-      </c>
-      <c r="N103" s="2"/>
-      <c r="O103" s="2"/>
+        <v>626</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>627</v>
+      </c>
       <c r="P103" t="s" s="2">
         <v>82</v>
       </c>
@@ -14691,11 +14483,13 @@
         <v>82</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y103" s="2"/>
+        <v>82</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>82</v>
+      </c>
       <c r="Z103" t="s" s="2">
-        <v>444</v>
+        <v>82</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>82</v>
@@ -14713,22 +14507,22 @@
         <v>82</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>445</v>
+        <v>506</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH103" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI103" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ103" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>446</v>
+        <v>189</v>
       </c>
       <c r="AL103" t="s" s="2">
         <v>82</v>
@@ -14737,7 +14531,7 @@
         <v>82</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>447</v>
+        <v>82</v>
       </c>
       <c r="AO103" t="s" s="2">
         <v>82</v>
@@ -14745,18 +14539,18 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>658</v>
+        <v>628</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
-        <v>449</v>
+        <v>82</v>
       </c>
       <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G104" t="s" s="2">
         <v>90</v>
@@ -14768,19 +14562,23 @@
         <v>82</v>
       </c>
       <c r="J104" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>104</v>
+        <v>219</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>450</v>
+        <v>629</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>451</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" s="2"/>
+        <v>630</v>
+      </c>
+      <c r="N104" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="O104" t="s" s="2">
+        <v>632</v>
+      </c>
       <c r="P104" t="s" s="2">
         <v>82</v>
       </c>
@@ -14792,7 +14590,7 @@
         <v>82</v>
       </c>
       <c r="T104" t="s" s="2">
-        <v>452</v>
+        <v>82</v>
       </c>
       <c r="U104" t="s" s="2">
         <v>82</v>
@@ -14804,13 +14602,11 @@
         <v>82</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>82</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="Y104" s="2"/>
       <c r="Z104" t="s" s="2">
-        <v>82</v>
+        <v>633</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>82</v>
@@ -14828,10 +14624,10 @@
         <v>82</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>453</v>
+        <v>628</v>
       </c>
       <c r="AG104" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH104" t="s" s="2">
         <v>90</v>
@@ -14843,16 +14639,16 @@
         <v>102</v>
       </c>
       <c r="AK104" t="s" s="2">
-        <v>454</v>
+        <v>634</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>82</v>
+        <v>635</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN104" t="s" s="2">
-        <v>455</v>
+        <v>636</v>
       </c>
       <c r="AO104" t="s" s="2">
         <v>82</v>
@@ -14860,10 +14656,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>659</v>
+        <v>637</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14883,21 +14679,23 @@
         <v>82</v>
       </c>
       <c r="J105" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>104</v>
+        <v>261</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>457</v>
+        <v>638</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>458</v>
+        <v>639</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="O105" s="2"/>
+        <v>640</v>
+      </c>
+      <c r="O105" t="s" s="2">
+        <v>641</v>
+      </c>
       <c r="P105" t="s" s="2">
         <v>82</v>
       </c>
@@ -14945,7 +14743,7 @@
         <v>82</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>460</v>
+        <v>637</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>80</v>
@@ -14960,16 +14758,16 @@
         <v>102</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>461</v>
+        <v>642</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>82</v>
+        <v>643</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN105" t="s" s="2">
-        <v>462</v>
+        <v>644</v>
       </c>
       <c r="AO105" t="s" s="2">
         <v>82</v>
@@ -14977,21 +14775,21 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>660</v>
+        <v>645</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
-        <v>82</v>
+        <v>646</v>
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H106" t="s" s="2">
         <v>82</v>
@@ -15000,21 +14798,21 @@
         <v>82</v>
       </c>
       <c r="J106" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>246</v>
+        <v>647</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>464</v>
+        <v>648</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>465</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" t="s" s="2">
-        <v>466</v>
-      </c>
+        <v>649</v>
+      </c>
+      <c r="N106" t="s" s="2">
+        <v>650</v>
+      </c>
+      <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
         <v>82</v>
       </c>
@@ -15026,7 +14824,7 @@
         <v>82</v>
       </c>
       <c r="T106" t="s" s="2">
-        <v>467</v>
+        <v>82</v>
       </c>
       <c r="U106" t="s" s="2">
         <v>82</v>
@@ -15062,13 +14860,13 @@
         <v>82</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>468</v>
+        <v>645</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH106" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI106" t="s" s="2">
         <v>82</v>
@@ -15077,16 +14875,16 @@
         <v>102</v>
       </c>
       <c r="AK106" t="s" s="2">
-        <v>331</v>
+        <v>651</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>469</v>
+        <v>652</v>
       </c>
       <c r="AO106" t="s" s="2">
         <v>82</v>
@@ -15094,10 +14892,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15117,20 +14915,22 @@
         <v>82</v>
       </c>
       <c r="J107" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>166</v>
+        <v>253</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>662</v>
+        <v>654</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N107" s="2"/>
+        <v>655</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>656</v>
+      </c>
       <c r="O107" t="s" s="2">
-        <v>664</v>
+        <v>657</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>82</v>
@@ -15155,13 +14955,13 @@
         <v>82</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>213</v>
+        <v>82</v>
       </c>
       <c r="Y107" t="s" s="2">
-        <v>665</v>
+        <v>82</v>
       </c>
       <c r="Z107" t="s" s="2">
-        <v>666</v>
+        <v>82</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>82</v>
@@ -15179,7 +14979,7 @@
         <v>82</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>661</v>
+        <v>653</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15194,16 +14994,16 @@
         <v>102</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>348</v>
+        <v>608</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>108</v>
+        <v>658</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>667</v>
+        <v>82</v>
       </c>
       <c r="AO107" t="s" s="2">
         <v>82</v>
@@ -15211,10 +15011,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15225,29 +15025,31 @@
         <v>80</v>
       </c>
       <c r="G108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="H108" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I108" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J108" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>253</v>
+        <v>496</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="N108" s="2"/>
+        <v>661</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>662</v>
+      </c>
       <c r="O108" t="s" s="2">
-        <v>671</v>
+        <v>663</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>82</v>
@@ -15296,22 +15098,22 @@
         <v>82</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH108" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>672</v>
+        <v>82</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>102</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>108</v>
@@ -15320,7 +15122,7 @@
         <v>82</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>674</v>
+        <v>82</v>
       </c>
       <c r="AO108" t="s" s="2">
         <v>82</v>
@@ -15328,10 +15130,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>675</v>
+        <v>665</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15354,13 +15156,13 @@
         <v>82</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>676</v>
+        <v>105</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>677</v>
+        <v>106</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -15411,7 +15213,7 @@
         <v>82</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>675</v>
+        <v>107</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15423,13 +15225,13 @@
         <v>82</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>678</v>
+        <v>108</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>82</v>
@@ -15443,14 +15245,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>679</v>
+        <v>666</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>82</v>
+        <v>110</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15469,20 +15271,18 @@
         <v>82</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>561</v>
+        <v>111</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>680</v>
+        <v>112</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>681</v>
+        <v>113</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="O110" t="s" s="2">
-        <v>683</v>
-      </c>
+        <v>114</v>
+      </c>
+      <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
         <v>82</v>
       </c>
@@ -15530,7 +15330,7 @@
         <v>82</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>679</v>
+        <v>118</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>80</v>
@@ -15542,13 +15342,13 @@
         <v>82</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>684</v>
+        <v>108</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>685</v>
+        <v>82</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>82</v>
@@ -15562,10 +15362,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>686</v>
+        <v>667</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>686</v>
+        <v>667</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15576,25 +15376,25 @@
         <v>80</v>
       </c>
       <c r="G111" t="s" s="2">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="H111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I111" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="J111" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>105</v>
+        <v>194</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>106</v>
+        <v>195</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -15645,22 +15445,22 @@
         <v>82</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>107</v>
+        <v>506</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH111" t="s" s="2">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="AI111" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ111" t="s" s="2">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="AL111" t="s" s="2">
         <v>82</v>
@@ -15677,21 +15477,21 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>687</v>
+        <v>668</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>110</v>
+        <v>82</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>82</v>
@@ -15700,19 +15500,19 @@
         <v>82</v>
       </c>
       <c r="J112" t="s" s="2">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>111</v>
+        <v>669</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>112</v>
+        <v>670</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>113</v>
+        <v>671</v>
       </c>
       <c r="N112" t="s" s="2">
-        <v>114</v>
+        <v>672</v>
       </c>
       <c r="O112" s="2"/>
       <c r="P112" t="s" s="2">
@@ -15762,31 +15562,31 @@
         <v>82</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>118</v>
+        <v>668</v>
       </c>
       <c r="AG112" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ112" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK112" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AL112" t="s" s="2">
         <v>108</v>
       </c>
-      <c r="AL112" t="s" s="2">
-        <v>82</v>
-      </c>
       <c r="AM112" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AN112" t="s" s="2">
-        <v>82</v>
+        <v>673</v>
       </c>
       <c r="AO112" t="s" s="2">
         <v>82</v>
@@ -15794,46 +15594,42 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>688</v>
+        <v>674</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
-        <v>689</v>
+        <v>82</v>
       </c>
       <c r="E113" s="2"/>
       <c r="F113" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="G113" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="H113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="I113" t="s" s="2">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="J113" t="s" s="2">
         <v>91</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>111</v>
+        <v>166</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>690</v>
+        <v>675</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>691</v>
-      </c>
-      <c r="N113" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O113" t="s" s="2">
-        <v>692</v>
-      </c>
+        <v>676</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
         <v>82</v>
       </c>
@@ -15857,13 +15653,13 @@
         <v>82</v>
       </c>
       <c r="X113" t="s" s="2">
-        <v>82</v>
+        <v>213</v>
       </c>
       <c r="Y113" t="s" s="2">
-        <v>82</v>
+        <v>676</v>
       </c>
       <c r="Z113" t="s" s="2">
-        <v>82</v>
+        <v>677</v>
       </c>
       <c r="AA113" t="s" s="2">
         <v>82</v>
@@ -15881,25 +15677,25 @@
         <v>82</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>571</v>
+        <v>674</v>
       </c>
       <c r="AG113" t="s" s="2">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="AH113" t="s" s="2">
-        <v>81</v>
+        <v>90</v>
       </c>
       <c r="AI113" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AJ113" t="s" s="2">
-        <v>119</v>
+        <v>102</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>189</v>
+        <v>678</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>82</v>
+        <v>108</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>82</v>
@@ -15908,1181 +15704,11 @@
         <v>82</v>
       </c>
       <c r="AO113" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>694</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="N114" t="s" s="2">
-        <v>696</v>
-      </c>
-      <c r="O114" t="s" s="2">
-        <v>697</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>148</v>
-      </c>
-      <c r="Y114" s="2"/>
-      <c r="Z114" t="s" s="2">
-        <v>698</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>693</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>699</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>700</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>701</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>261</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>703</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>704</v>
-      </c>
-      <c r="N115" t="s" s="2">
-        <v>705</v>
-      </c>
-      <c r="O115" t="s" s="2">
-        <v>706</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>702</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>707</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>708</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>709</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>711</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>712</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>713</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>714</v>
-      </c>
-      <c r="N116" t="s" s="2">
-        <v>715</v>
-      </c>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>710</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>716</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>717</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>719</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>720</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>721</v>
-      </c>
-      <c r="O117" t="s" s="2">
-        <v>722</v>
-      </c>
-      <c r="P117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>718</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>723</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>725</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>726</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>727</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>728</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>724</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>729</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>730</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N119" s="2"/>
-      <c r="O119" s="2"/>
-      <c r="P119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>731</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>732</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>195</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>734</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>735</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>736</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>737</v>
-      </c>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>733</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>738</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>91</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>740</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>741</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>742</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>739</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>743</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AO123" t="s" s="2">
         <v>82</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AO123">
+  <autoFilter ref="A1:AO113">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17092,7 +15718,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI122">
+  <conditionalFormatting sqref="A2:AI112">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
